--- a/BKC01D.xlsx
+++ b/BKC01D.xlsx
@@ -124,7 +124,7 @@
     <t>20140018</t>
   </si>
   <si>
-    <t>IDM BB.WIPE RM 2X50S</t>
+    <t>IDM BBY RC BD 2X50 S</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
@@ -133,13 +133,13 @@
     <t>20138272</t>
   </si>
   <si>
-    <t>LRST BB.WIPE SB 2X50</t>
+    <t>LRSST BW SB B 2X50 S</t>
   </si>
   <si>
     <t>20138273</t>
   </si>
   <si>
-    <t>LRST BB.WIPE AF 2X50</t>
+    <t>LRSST BW AQ B 2X50 S</t>
   </si>
   <si>
     <t>20001546</t>
@@ -148,12 +148,30 @@
     <t>MITU G/P BLUE 2x50'S</t>
   </si>
   <si>
+    <t>20035113</t>
+  </si>
+  <si>
+    <t>MITU WIPE BB 2x40'S</t>
+  </si>
+  <si>
+    <t>20001061</t>
+  </si>
+  <si>
+    <t>MITU G/P PINK 2x50'S</t>
+  </si>
+  <si>
     <t>20071105</t>
   </si>
   <si>
     <t>MITU TIS. PF 2x50'S</t>
   </si>
   <si>
+    <t>20016864</t>
+  </si>
+  <si>
+    <t>CSSN BW RFRSH 2/3X45</t>
+  </si>
+  <si>
     <t>20087203</t>
   </si>
   <si>
@@ -172,124 +190,106 @@
     <t>MP BB WIPES N/FR BDD</t>
   </si>
   <si>
+    <t>20082446</t>
+  </si>
+  <si>
+    <t>MP BB WIPES PRF BDD</t>
+  </si>
+  <si>
     <t>20138144</t>
   </si>
   <si>
     <t>KODOMO WPS H&amp;M 2X50S</t>
   </si>
   <si>
-    <t>20035113</t>
-  </si>
-  <si>
-    <t>MITU WIPE BB 2x40'S</t>
-  </si>
-  <si>
-    <t>20001061</t>
-  </si>
-  <si>
-    <t>MITU G/P PINK 2x50'S</t>
+    <t>20105698</t>
+  </si>
+  <si>
+    <t>ZWTSL KIDS BB C&amp;F280</t>
+  </si>
+  <si>
+    <t>20103266</t>
+  </si>
+  <si>
+    <t>MB KIDS S&amp;C H&amp;F 180</t>
+  </si>
+  <si>
+    <t>20113915</t>
+  </si>
+  <si>
+    <t>MB KIDS S&amp;C SOFT 180</t>
+  </si>
+  <si>
+    <t>20096095</t>
+  </si>
+  <si>
+    <t>KDOMO SH&amp;CON STR 200</t>
+  </si>
+  <si>
+    <t>20090400</t>
+  </si>
+  <si>
+    <t>KDOMO B.WASH STR 200</t>
+  </si>
+  <si>
+    <t>20113805</t>
+  </si>
+  <si>
+    <t>KDOMO B.WASH ORG 200</t>
+  </si>
+  <si>
+    <t>20143473</t>
+  </si>
+  <si>
+    <t>B&amp;B S&amp;C GLY SH200+50</t>
+  </si>
+  <si>
+    <t>20143316</t>
+  </si>
+  <si>
+    <t>ZWTSL B/B ANTIBAC300</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20012094</t>
+  </si>
+  <si>
+    <t>ZWITSAL B/BATH MH300</t>
+  </si>
+  <si>
+    <t>20143472</t>
+  </si>
+  <si>
+    <t>BB HAIR&amp;BW PMP240+60</t>
+  </si>
+  <si>
+    <t>20135607</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC LVELY100</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>20016864</t>
-  </si>
-  <si>
-    <t>CSSN BW RFRSH 2/3X45</t>
+    <t>20113917</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC SWT 100</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>20082446</t>
-  </si>
-  <si>
-    <t>MP BB WIPES PRF BDD</t>
+    <t>20113918</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC FRSH100</t>
   </si>
   <si>
     <t>13</t>
-  </si>
-  <si>
-    <t>20105698</t>
-  </si>
-  <si>
-    <t>ZWTSL KIDS BB C&amp;F280</t>
-  </si>
-  <si>
-    <t>20103266</t>
-  </si>
-  <si>
-    <t>MB KIDS S&amp;C H&amp;F 180</t>
-  </si>
-  <si>
-    <t>20113915</t>
-  </si>
-  <si>
-    <t>MB KIDS S&amp;C SOFT 180</t>
-  </si>
-  <si>
-    <t>20096095</t>
-  </si>
-  <si>
-    <t>KDOMO SH&amp;CON STR 200</t>
-  </si>
-  <si>
-    <t>20090400</t>
-  </si>
-  <si>
-    <t>KDOMO B.WASH STR 200</t>
-  </si>
-  <si>
-    <t>20113805</t>
-  </si>
-  <si>
-    <t>KDOMO B.WASH ORG 200</t>
-  </si>
-  <si>
-    <t>20143473</t>
-  </si>
-  <si>
-    <t>B&amp;B S&amp;C GLY SH200+50</t>
-  </si>
-  <si>
-    <t>20143316</t>
-  </si>
-  <si>
-    <t>ZWTSL B/B ANTIBAC300</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20012094</t>
-  </si>
-  <si>
-    <t>ZWITSAL B/BATH MH300</t>
-  </si>
-  <si>
-    <t>20143472</t>
-  </si>
-  <si>
-    <t>BB HAIR&amp;BW PMP240+60</t>
-  </si>
-  <si>
-    <t>20135607</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC LVELY100</t>
-  </si>
-  <si>
-    <t>20113917</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC SWT 100</t>
-  </si>
-  <si>
-    <t>20113918</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC FRSH100</t>
   </si>
   <si>
     <t>20143470</t>
@@ -1481,10 +1481,10 @@
         <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1501,10 +1501,10 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1521,10 +1521,10 @@
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1541,10 +1541,10 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1561,10 +1561,10 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1581,7 +1581,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>9</v>
@@ -1601,18 +1601,18 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1621,18 +1621,18 @@
         <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1641,18 +1641,18 @@
         <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1689,10 +1689,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1749,10 +1749,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1769,10 +1769,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1804,15 +1804,15 @@
         <v>29</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1829,10 +1829,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1861,7 +1861,7 @@
         <v>12</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>9</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1881,7 +1881,7 @@
         <v>12</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>9</v>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1901,7 +1901,7 @@
         <v>12</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>9</v>
@@ -2241,7 +2241,7 @@
         <v>15</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>132</v>
@@ -2261,7 +2261,7 @@
         <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>132</v>
@@ -2281,7 +2281,7 @@
         <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>132</v>
@@ -2541,7 +2541,7 @@
         <v>18</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>132</v>
@@ -2561,7 +2561,7 @@
         <v>18</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>132</v>
@@ -2581,7 +2581,7 @@
         <v>18</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -2801,7 +2801,7 @@
         <v>22</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2821,7 +2821,7 @@
         <v>22</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>9</v>
@@ -2841,7 +2841,7 @@
         <v>22</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>9</v>
@@ -2964,7 +2964,7 @@
         <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3141,7 +3141,7 @@
         <v>26</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>9</v>
@@ -3361,7 +3361,7 @@
         <v>29</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3381,7 +3381,7 @@
         <v>29</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>

--- a/BKC01D.xlsx
+++ b/BKC01D.xlsx
@@ -64,7 +64,7 @@
     <t>20049716</t>
   </si>
   <si>
-    <t>MITU B/WPS RF.LM 10S</t>
+    <t>MITU B/WPS RF.LM3X10</t>
   </si>
   <si>
     <t>5</t>

--- a/BKC01D.xlsx
+++ b/BKC01D.xlsx
@@ -169,13 +169,13 @@
     <t>20016864</t>
   </si>
   <si>
-    <t>CSSN BW RFRSH 2/3X45</t>
+    <t>CSSN BBY R P 3X45'S</t>
   </si>
   <si>
     <t>20087203</t>
   </si>
   <si>
-    <t>CSSN BW FRS&amp;N 2/3X45</t>
+    <t>CSSN BW BN P 3X45'S</t>
   </si>
   <si>
     <t>20113913</t>
@@ -367,7 +367,7 @@
     <t>20002133</t>
   </si>
   <si>
-    <t>IDM CT.BUD BABY R100</t>
+    <t>IDM C.BUDS BBY 100'S</t>
   </si>
   <si>
     <t>PT</t>
@@ -376,13 +376,13 @@
     <t>20098361</t>
   </si>
   <si>
-    <t>IDM CT.BUDS SPRL 100</t>
+    <t>IDM C.BUDS SPL 100'S</t>
   </si>
   <si>
     <t>20115786</t>
   </si>
   <si>
-    <t>IDM CTN.BUDS RFL 100</t>
+    <t>IDM C.BUDS RFL 100'S</t>
   </si>
   <si>
     <t>20115501</t>
